--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486496_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486496_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8457</v>
+        <v>4.3764</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9639</v>
+        <v>5.0913</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8818</v>
+        <v>-0.7149</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.663</v>
+        <v>4.6646</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2645</v>
+        <v>2.5425</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3984</v>
+        <v>2.122</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4878</v>
+        <v>6.4672</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3348</v>
+        <v>3.5404</v>
       </c>
       <c r="L2" t="n">
-        <v>0.153</v>
+        <v>2.9269</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1508</v>
+        <v>-1.8027</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5994</v>
+        <v>-0.9978</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5514</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5516</v>
+        <v>0.6243</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3461</v>
+        <v>-0.2884</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2055</v>
+        <v>0.9127</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8695</v>
+        <v>-1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5209</v>
+        <v>3.7793</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4208</v>
+        <v>2.1441</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8999</v>
+        <v>1.6352</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6646</v>
+        <v>-0.663</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5425</v>
+        <v>-0.2645</v>
       </c>
       <c r="I3" t="n">
-        <v>2.122</v>
+        <v>-0.3984</v>
       </c>
       <c r="J3" t="n">
-        <v>6.4672</v>
+        <v>0.4878</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5404</v>
+        <v>0.3348</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9269</v>
+        <v>0.153</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8027</v>
+        <v>-1.1508</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9978</v>
+        <v>-0.5994</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.5514</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2312</v>
+        <v>1.4853</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9589</v>
+        <v>0.5264</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7277</v>
+        <v>0.9589</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.13</v>
+        <v>1.8695</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.13</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0747</v>
+        <v>2.6644</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6787</v>
+        <v>2.1451</v>
       </c>
       <c r="F4" t="n">
-        <v>0.396</v>
+        <v>0.5193</v>
       </c>
       <c r="G4" t="n">
         <v>3.342</v>
@@ -766,13 +766,13 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1253</v>
+        <v>0.715</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4627</v>
+        <v>-0.0709</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6626</v>
+        <v>0.7859</v>
       </c>
       <c r="V4" t="n">
         <v>0.5649999999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2958</v>
+        <v>1.6216</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2975</v>
+        <v>1.3497</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9983</v>
+        <v>0.2719</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.1792</v>
+        <v>-1.666</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4628</v>
+        <v>0.1826</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7164</v>
+        <v>-1.8487</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.042</v>
+        <v>-0.2458</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.195</v>
+        <v>1.0315</v>
       </c>
       <c r="L5" t="n">
-        <v>0.153</v>
+        <v>-1.2773</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1372</v>
+        <v>-1.4202</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2679</v>
+        <v>-0.8488</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8694</v>
+        <v>-0.5714</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9976</v>
+        <v>1.4399</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1893</v>
+        <v>0.2704</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8083</v>
+        <v>1.1695</v>
       </c>
       <c r="V5" t="n">
-        <v>1.13</v>
+        <v>0.7602</v>
       </c>
       <c r="W5" t="n">
         <v>1.3252</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5638</v>
+        <v>0.5913</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0145</v>
+        <v>-1.3939</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5493</v>
+        <v>1.9851</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.666</v>
+        <v>-1.1136</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1826</v>
+        <v>0.292</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8487</v>
+        <v>-1.4056</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2458</v>
+        <v>-0.4409</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0315</v>
+        <v>0.6268</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2773</v>
+        <v>-1.0678</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4202</v>
+        <v>-0.6727</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8488</v>
+        <v>-0.3348</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5714</v>
+        <v>-0.3379</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3821</v>
+        <v>1.0524</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0649</v>
+        <v>0.1346</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4469</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0553</v>
+        <v>0.5809</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1329</v>
+        <v>-0.6024</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0776</v>
+        <v>1.1833</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1136</v>
+        <v>-2.1792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.292</v>
+        <v>-1.4628</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4056</v>
+        <v>-0.7164</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4409</v>
+        <v>-1.042</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6268</v>
+        <v>-1.195</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.0678</v>
+        <v>0.153</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6727</v>
+        <v>-1.1372</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3348</v>
+        <v>-0.2679</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3379</v>
+        <v>-0.8694</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4058</v>
+        <v>2.2826</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6044</v>
+        <v>1.2894</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0103</v>
+        <v>0.9932</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.114</v>
+        <v>0.3446</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0622</v>
+        <v>0.273</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0517</v>
+        <v>0.0716</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2767</v>
@@ -1078,13 +1078,13 @@
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0548</v>
+        <v>0.4038</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.137</v>
+        <v>0.1983</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0822</v>
+        <v>0.2055</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1649</v>
+        <v>0.1887</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2981</v>
+        <v>-0.0061</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1332</v>
+        <v>0.1949</v>
       </c>
       <c r="G9" t="n">
         <v>-0.367</v>
@@ -1156,13 +1156,13 @@
         <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2329</v>
+        <v>0.1208</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6165</v>
+        <v>-0.3245</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3836</v>
+        <v>0.4452</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.33</v>
+        <v>-0.4349</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6651</v>
+        <v>-0.7083</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3351</v>
+        <v>0.2735</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4569</v>
@@ -1234,13 +1234,13 @@
         <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9094</v>
+        <v>0.8045</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1454</v>
+        <v>-0.1887</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0548</v>
+        <v>0.9932</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1182</v>
+        <v>-1.715</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1808</v>
+        <v>-2.867</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0626</v>
+        <v>1.152</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8817</v>
+        <v>0.4974</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8092</v>
+        <v>-0.3743</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0725</v>
+        <v>0.8718</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6138</v>
+        <v>1.4706</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0547</v>
+        <v>0.4745</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6686</v>
+        <v>0.9961</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2679</v>
+        <v>-0.9732</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8639</v>
+        <v>-0.8488</v>
       </c>
       <c r="O11" t="n">
-        <v>0.596</v>
+        <v>-0.1243</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.87</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3665</v>
+        <v>0.6375</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4795</v>
+        <v>-0.1826</v>
       </c>
       <c r="U11" t="n">
-        <v>0.113</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3491</v>
+        <v>-1.938</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5628</v>
+        <v>-2.0006</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2137</v>
+        <v>0.0626</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4974</v>
+        <v>-0.8817</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3743</v>
+        <v>-0.8092</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8718</v>
+        <v>-0.0725</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4706</v>
+        <v>-0.6138</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4745</v>
+        <v>0.0547</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9961</v>
+        <v>-0.6686</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9732</v>
+        <v>-0.2679</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8488</v>
+        <v>-0.8639</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1243</v>
+        <v>0.596</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.0451</v>
+        <v>-0.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R12" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0034</v>
+        <v>-0.1863</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8784</v>
+        <v>-0.2992</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8818</v>
+        <v>0.113</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2018</v>
+        <v>-3.407</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1802</v>
+        <v>-3.4469</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0217</v>
+        <v>0.04</v>
       </c>
       <c r="G13" t="n">
         <v>-0.6449</v>
@@ -1468,13 +1468,13 @@
         <v>0.435</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2706</v>
+        <v>0.0655</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0769</v>
+        <v>-0.3437</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3475</v>
+        <v>0.4092</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.967599999999999</v>
+        <v>6.652299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7066999999999997</v>
+        <v>-0.02199999999999935</v>
       </c>
       <c r="F14" t="n">
-        <v>6.6743</v>
+        <v>6.6745</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7449999999999994</v>
+        <v>-0.7449999999999998</v>
       </c>
       <c r="H14" t="n">
         <v>2.2352</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.9801</v>
+        <v>-2.980099999999999</v>
       </c>
       <c r="J14" t="n">
         <v>10.4644</v>
@@ -1525,7 +1525,7 @@
         <v>10.3885</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07579999999999984</v>
+        <v>0.07579999999999973</v>
       </c>
       <c r="M14" t="n">
         <v>-11.2095</v>
@@ -1537,7 +1537,7 @@
         <v>-3.0562</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.437800000000001</v>
+        <v>-5.4378</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.3129</v>
@@ -1546,10 +1546,10 @@
         <v>10.8751</v>
       </c>
       <c r="S14" t="n">
-        <v>8.760399999999999</v>
+        <v>9.4453</v>
       </c>
       <c r="T14" t="n">
-        <v>0.03619999999999965</v>
+        <v>0.7211</v>
       </c>
       <c r="U14" t="n">
         <v>8.7242</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. LOPEZ SANTANA</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3368</v>
+        <v>3.1527</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2991</v>
+        <v>0.9648</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0378</v>
+        <v>2.1878</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5799</v>
+        <v>1.1399</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3104</v>
+        <v>0.9064</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2695</v>
+        <v>0.2335</v>
       </c>
       <c r="J15" t="n">
-        <v>4.671</v>
+        <v>1.7641</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3417</v>
+        <v>2.0868</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3293</v>
+        <v>-0.3227</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0911</v>
+        <v>-0.6241</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0313</v>
+        <v>-1.1803</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0598</v>
+        <v>0.5562</v>
       </c>
       <c r="P15" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8276</v>
+        <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1131</v>
+        <v>-0.5528</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5444</v>
+        <v>-0.9722</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4313</v>
+        <v>0.4194</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.3904</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.3904</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>J. LOPEZ SANTANA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8919</v>
+        <v>2.8115</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8531</v>
+        <v>1.9638</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0388</v>
+        <v>0.8477</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1399</v>
+        <v>3.5799</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9064</v>
+        <v>0.3104</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2335</v>
+        <v>3.2695</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7641</v>
+        <v>4.671</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0868</v>
+        <v>1.3417</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3227</v>
+        <v>3.3293</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6241</v>
+        <v>-1.0911</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1803</v>
+        <v>-1.0313</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5562</v>
+        <v>-0.0598</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1751</v>
+        <v>0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3926</v>
+        <v>2.8276</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8136</v>
+        <v>-0.6384</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0839</v>
+        <v>-0.8796</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2704</v>
+        <v>0.2412</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3904</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3904</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8404</v>
+        <v>1.8597</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0943</v>
+        <v>1.206</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7461</v>
+        <v>0.6536</v>
       </c>
       <c r="G17" t="n">
         <v>1.1125</v>
@@ -1780,13 +1780,13 @@
         <v>2.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0122</v>
+        <v>-0.9929</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1524</v>
+        <v>-1.0407</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1402</v>
+        <v>0.0478</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>K. WEBSTER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0349</v>
+        <v>1.2357</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0376</v>
+        <v>1.1071</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9973</v>
+        <v>0.1286</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4304</v>
+        <v>3.6857</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1899</v>
+        <v>1.6059</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7595</v>
+        <v>2.0798</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4076</v>
+        <v>4.8263</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3422</v>
+        <v>3.2182</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.9347</v>
+        <v>1.6081</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9771</v>
+        <v>-1.1406</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1523</v>
+        <v>-1.6123</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8248</v>
+        <v>0.4717</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7401</v>
+        <v>-0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.6101</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1356</v>
+        <v>-0.8851</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3699</v>
+        <v>-1.1092</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2343</v>
+        <v>0.2241</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. WEBSTER</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9133</v>
+        <v>1.0992</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9953</v>
+        <v>0.2612</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.082</v>
+        <v>0.838</v>
       </c>
       <c r="G19" t="n">
-        <v>3.6857</v>
+        <v>0.4304</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6059</v>
+        <v>2.1899</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0798</v>
+        <v>-1.7595</v>
       </c>
       <c r="J19" t="n">
-        <v>4.8263</v>
+        <v>1.4076</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2182</v>
+        <v>2.3422</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6081</v>
+        <v>-0.9347</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1406</v>
+        <v>-0.9771</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6123</v>
+        <v>-0.1523</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4717</v>
+        <v>-0.8248</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.6101</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2075</v>
+        <v>-1.0713</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2209</v>
+        <v>-1.1464</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0134</v>
+        <v>0.0751</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7283</v>
+        <v>-1.9132</v>
       </c>
       <c r="E20" t="n">
         <v>-1.8085</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0803</v>
+        <v>-0.1047</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4934</v>
@@ -2014,13 +2014,13 @@
         <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0702</v>
+        <v>-0.1148</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3425</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4127</v>
+        <v>0.2277</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0749</v>
+        <v>-2.1828</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7746</v>
+        <v>-1.2216</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3002</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6774</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9624</v>
+        <v>-1.0704</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1454</v>
+        <v>-0.5924</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.478</v>
       </c>
       <c r="V21" t="n">
         <v>1.13</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8085</v>
+        <v>-2.9737</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7563</v>
+        <v>-2.5328</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0522</v>
+        <v>-0.4409</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6716</v>
@@ -2170,13 +2170,13 @@
         <v>3.0451</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.5518</v>
+        <v>-1.7169</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.7004</v>
+        <v>-1.4769</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8514</v>
+        <v>-0.2401</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3252</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8088</v>
+        <v>-3.6855</v>
       </c>
       <c r="E23" t="n">
         <v>-2.5353</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2734</v>
+        <v>-1.1501</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9867</v>
@@ -2248,13 +2248,13 @@
         <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4093</v>
+        <v>-0.286</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3425</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0668</v>
+        <v>0.0565</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3252</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5644</v>
+        <v>-4.6261</v>
       </c>
       <c r="E24" t="n">
         <v>-3.5139</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0505</v>
+        <v>-1.1121</v>
       </c>
       <c r="G24" t="n">
         <v>-3.3743</v>
@@ -2326,13 +2326,13 @@
         <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6251</v>
+        <v>-0.6868</v>
       </c>
       <c r="T24" t="n">
         <v>-0.822</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1968</v>
+        <v>0.1352</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5649999999999999</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.967600000000001</v>
+        <v>-5.2225</v>
       </c>
       <c r="E25" t="n">
         <v>-6.1092</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1419999999999999</v>
+        <v>0.8867000000000003</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7449999999999992</v>
+        <v>0.745000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>-2.2352</v>
@@ -2383,7 +2383,7 @@
         <v>8.1533</v>
       </c>
       <c r="L25" t="n">
-        <v>3.0561</v>
+        <v>3.056099999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-10.4644</v>
@@ -2392,10 +2392,10 @@
         <v>-10.3886</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.07589999999999993</v>
+        <v>-0.07589999999999987</v>
       </c>
       <c r="P25" t="n">
-        <v>5.437900000000001</v>
+        <v>5.437899999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-10.8752</v>
@@ -2404,13 +2404,13 @@
         <v>16.3131</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.760400000000001</v>
+        <v>-8.0154</v>
       </c>
       <c r="T25" t="n">
-        <v>-8.724299999999999</v>
+        <v>-8.724399999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.03610000000000013</v>
+        <v>0.7088999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-3.39</v>
